--- a/04_DESIGN_TABLES/DesignTable_1502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1502.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,7 +555,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Air-Way s114 only (double-pass 16 rows)</t>
+          <t>Air-Way s114 only (double-pass 16 rows) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the round collar of the female pipe leg (0.26, measured on the -04 / -06 / -08 / -16 forgings, applied to -02) and the NPSM swivel end (Brennan 1404 STEPs); the sizes of the part are Air-Way's</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-10-02 cross-check, Brennan TFA catalog p21 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf, table TFA-p021-t01 in tools/_out/brennan_catalog_20261001/catalog_verified.json, verified; re-read from the PDF text layer 2026-10-02) 1502-02-02-FG: DIFFERS on N3 0.75 vs L 0.660; M1 0.74 vs M 0.800; W3 0.89 vs M1 0.940; D 0.13 vs A2 DRILL 0.110 (Air-Way vs Brennan); agrees on CHEX 0.56, C1HEX 0.56 (within rounding) - built to Air-Way (OMi gives no dimensions for this part; no size is taken from Brennan (user ruling 2026-10-08: Brennan for shape only)) - flag for OMi</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -745,6 +750,11 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>Air-Way s114 only (double-pass 16 rows)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-10-02 cross-check, Brennan TFA catalog p21 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf, table TFA-p021-t01 in tools/_out/brennan_catalog_20261001/catalog_verified.json, verified; re-read from the PDF text layer 2026-10-02) 1502-04-04-FG: DIFFERS on N3 0.94 vs L 0.880; M1 0.78 vs M 0.990; W3 0.97 vs M1 1.180; C1HEX 0.69 vs Y FLATS 0.750 (Air-Way vs Brennan); agrees on CHEX 0.69, D 0.22 (within rounding) - modelled to Air-Way (OMi gives no dimensions for this part; Brennan-only values wait for Q-BRENNAN-ONLY) - NOT BUILT: gen_tee BLOCKS this row (review 2026-10-02): with Air-Way M1 0.78 the swivel body face (0.39 = M1 - the Brennan 1404-04 body-to-tip 0.39, ASSUMED for the elbow) lies inside the hex corner radius (0.398 = C1HEX 0.69 / sqrt3), so the pipe-leg hex arm corner would stand 0.008 beyond it outside the swivel neck; Brennan faces that off at the body face (6500-05-05-FG STEP) and the 90 deg elbow has no facing cut. Brennan's own -04-04-FG (M 0.99, Y FLATS 0.750) would put the body face at about 0.60 with the same body-to-tip, clear of its corner radius 0.433 - flag for OMi</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_1502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1502.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1542,24 +1547,56 @@
           <t>1502-06-06-FG</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.675</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>1502-06-06-FG</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 3/8-18 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-06-06-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 0d65652c456fb904...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1570,6 +1607,11 @@
       <c r="Q19" t="inlineStr">
         <is>
           <t>1502-06-06-FG</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -1616,24 +1658,56 @@
           <t>1502-12-08-FG</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.84</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>1502-12-08-FG</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 1/2-14 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-12-08-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 05173adef898c6c2...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1644,6 +1718,11 @@
       <c r="Q21" t="inlineStr">
         <is>
           <t>1502-12-08-FG</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -1653,24 +1732,56 @@
           <t>1502-12-12-FG</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.05</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>1502-12-12-FG</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 3/4-14 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-12-12-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 541b6ec909ac5ef7...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1681,6 +1792,11 @@
       <c r="Q22" t="inlineStr">
         <is>
           <t>1502-12-12-FG</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -1690,24 +1806,56 @@
           <t>1502-16-16-FG</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.315</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>1502-16-16-FG</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A NPTF) x 1-11 1/2 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N3@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "L LGTH" = "1.620" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); M1@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "M LGTH" = "1.730" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel stem tip (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); W3@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "M1 LGTH" = "2.080" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); CHEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); C1HEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - body hex (forged flats) (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); D@BORE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-16-16-FG col "A2 DRILL" = "0.780" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 309.7, page verified True) [Brennan = yes 2026-10-18] - swivel stem bore (column pairing confirmed on the pilot 1502-08-08-FG STEP, where all six catalog values equal the STEP, and on the 6 OMi 2026-10-18 drawings of this series); TAPDRILL@BORE: end library: tap drill of the -16 female NPTF port = 1.14 (gen_straight2 FPT[16] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-12-16) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library]; THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -16 NPSM swivel thread = 1.315 (ASME B1.20.1 pipe OD, ms51500.py NPTF[16]; the value every 1405 / 1502 row carries for its NPSM end) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes; = OMi WebsitePartsInfo2026 Items Side 1 / Side 2 Thread and Brennan TFA p.21 A1 NPTF / A2 NPSM "1-11-1/2"</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1718,6 +1866,11 @@
       <c r="Q23" t="inlineStr">
         <is>
           <t>1502-16-16-FG</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1727,24 +1880,56 @@
           <t>1502-20-20-FG</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.66</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>1502-20-20-FG</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A NPTF) x 1 1/4-11 1/2 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-20-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-20-20-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 9ec6af161e958a81...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -1755,6 +1940,11 @@
       <c r="Q24" t="inlineStr">
         <is>
           <t>1502-20-20-FG</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -1764,24 +1954,56 @@
           <t>1502-24-24-FG</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.559</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.9</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>1502-24-24-FG</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 (A NPTF) x 1 1/2-11 1/2 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-24-24 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-24-24-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 2de88b184d18f1f4...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -1792,6 +2014,11 @@
       <c r="Q25" t="inlineStr">
         <is>
           <t>1502-24-24-FG</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -1801,24 +2028,56 @@
           <t>1502-32-32-FG</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.375</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>1502-32-32-FG</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2-11 1/2 (A NPTF) x 2-11 1/2 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-32-32 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-32-32 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_a/1502-32-32-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 faca6632b6a167d4...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -1829,6 +2088,11 @@
       <c r="Q26" t="inlineStr">
         <is>
           <t>1502-32-32-FG</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_1502.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1502.xlsx
@@ -714,10 +714,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="D6" t="n">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="E6" t="n">
         <v>0.6899999999999999</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Air-Way s114 only (double-pass 16 rows)</t>
+          <t>[BRENNAN-CELL 2026-10-21: M1@DRIVE, W3@HEX] Air-Way s114 only (double-pass 16 rows) | M1@DRIVE 0.99 / W3@HEX 1.18: Brennan TFA catalog p.21 TFA-p021-t01 row 1502-04-04-FG "M LGTH" 0.990 / "M1 LGTH" 1.180 - Air-Way M1 0.78 / W3 0.97 cannot be built (swivel body face inside the hex corner), user rule 2026-10-20 Q1 "use brennans"; the other cells stay Air-Way s114</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-02 cross-check, Brennan TFA catalog p21 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf, table TFA-p021-t01 in tools/_out/brennan_catalog_20261001/catalog_verified.json, verified; re-read from the PDF text layer 2026-10-02) 1502-04-04-FG: DIFFERS on N3 0.94 vs L 0.880; M1 0.78 vs M 0.990; W3 0.97 vs M1 1.180; C1HEX 0.69 vs Y FLATS 0.750 (Air-Way vs Brennan); agrees on CHEX 0.69, D 0.22 (within rounding) - modelled to Air-Way (OMi gives no dimensions for this part; Brennan-only values wait for Q-BRENNAN-ONLY) - NOT BUILT: gen_tee BLOCKS this row (review 2026-10-02): with Air-Way M1 0.78 the swivel body face (0.39 = M1 - the Brennan 1404-04 body-to-tip 0.39, ASSUMED for the elbow) lies inside the hex corner radius (0.398 = C1HEX 0.69 / sqrt3), so the pipe-leg hex arm corner would stand 0.008 beyond it outside the swivel neck; Brennan faces that off at the body face (6500-05-05-FG STEP) and the 90 deg elbow has no facing cut. Brennan's own -04-04-FG (M 0.99, Y FLATS 0.750) would put the body face at about 0.60 with the same body-to-tip, clear of its corner radius 0.433 - flag for OMi</t>
+          <t>2026-10-02 cross-check, Brennan TFA catalog p21 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf, table TFA-p021-t01 in tools/_out/brennan_catalog_20261001/catalog_verified.json, verified; re-read from the PDF text layer 2026-10-02) 1502-04-04-FG: DIFFERS on N3 0.94 vs L 0.880; M1 0.78 vs M 0.990; W3 0.97 vs M1 1.180; C1HEX 0.69 vs Y FLATS 0.750 (Air-Way vs Brennan); agrees on CHEX 0.69, D 0.22 (within rounding) - modelled to Air-Way (OMi gives no dimensions for this part; Brennan-only values wait for Q-BRENNAN-ONLY) - NOT BUILT: gen_tee BLOCKS this row (review 2026-10-02): with Air-Way M1 0.78 the swivel body face (0.39 = M1 - the Brennan 1404-04 body-to-tip 0.39, ASSUMED for the elbow) lies inside the hex corner radius (0.398 = C1HEX 0.69 / sqrt3), so the pipe-leg hex arm corner would stand 0.008 beyond it outside the swivel neck; Brennan faces that off at the body face (6500-05-05-FG STEP) and the 90 deg elbow has no facing cut. Brennan's own -04-04-FG (M 0.99, Y FLATS 0.750) would put the body face at about 0.60 with the same body-to-tip, clear of its corner radius 0.433 - flag for OMi | 2026-10-21 batch 19 C (staged): M1@DRIVE 0.78 -&gt; 0.99 and W3@HEX 0.97 -&gt; 1.18 (Brennan TFA p21) by the Q1 rule (Air-Way value not buildable -&gt; Brennan); the row now generates. Alternative: all four differing cells Brennan (N3 0.88, C1HEX 0.75 too) - also generates (C_ownstep/checks/test_1502-04-04-FG.txt). Tell the user these cells</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -770,6 +770,11 @@
       <c r="Q6" t="inlineStr">
         <is>
           <t>1502-04-04-FG</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1621,24 +1626,56 @@
           <t>1502-08-08-FG</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.84</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>1502-08-08-FG</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF) x 1/2-14 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1502-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_1502-08-08-FG.stp, every value equal to the catalog within 0.005); end details from the end library: N3@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "L LGTH" = "1.23" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the female NPTF port face; own STEP: port face 1.23 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); M1@DRIVE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "M LGTH" = "1.24" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel stem tip; own STEP: stem bore runs to 1.24 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); W3@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "M1 LGTH" = "1.52" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face; own STEP: nut face 1.52 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); CHEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "C HEX" = "1.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; own STEP: nut A/F 1.000 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py), npsm.py); C1HEX@HEX: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - body hex (forged flats); own STEP: body A/F 1.062, corner radius 0.6131 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); D@BORE: Brennan TFA catalog p.21 table TFA-p021-t01 "1502-FG FP-FPS 90 DEG ELBOW" row 1502-08-08-FG col "A2 DRILL" = "0.460" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 249.2, page verified True) [Brennan = yes 2026-10-18] - swivel stem bore; own STEP: bore 0.460 (C_ownstep/measure/1502-08-08-FG.txt (fgelbow.py / npsm.py)); TAPDRILL@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718 behind a 0.75 tapered port - the end library value is kept as on every sibling); THDMAJ_A@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -08 NPSM swivel thread = 0.84 (ASME B1.20.1 pipe OD, ms51500.py NPTF[8]; the value every 1405 / 1502 row carries for its NPSM end) [Q-TRANSFER-ENDLIB yes 2026-10-08]</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1502-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 1502-8-8 (plain): N3 1.25 W3 1.33 M1 1.00 CHEX 1.00 C1HEX 1.00 TAPDRILL 0.70 D 0.45 (differs from the forged part on N3 / W3 / M1 / C1HEX)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1649,6 +1686,11 @@
       <c r="Q20" t="inlineStr">
         <is>
           <t>1502-08-08-FG</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
